--- a/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
@@ -950,7 +950,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Daily: one row per MONTH (dated the 1st), MWh in the month (EPPO publishes GWh, x1,000). Gas, Coal (coal + lignite; Lignite_MWh shown separately as well), Oil (fuel oil + diesel), Hydro, Other = EPPO 'Renewable Energy' (solar, wind, biomass, biogas, waste - EPPO does not split it). Total_MWh = domestic generation (sum of those). Imports_MWh = imported electricity (Lao PDR hydro, some Malaysia), not in Total_MWh.</t>
+          <t>Daily: one row per MONTH (dated the 1st), MWh in the month (EPPO publishes GWh, x1,000). Gas, Coal (coal + lignite), Oil (fuel oil + diesel), Hydro, Other = EPPO 'Renewable Energy' (solar, wind, biomass, biogas, waste - EPPO does not split it). Total_MWh = domestic generation (sum of those). Imports_MWh = imported electricity (Lao PDR hydro, some Malaysia), not in Total_MWh.</t>
         </is>
       </c>
     </row>
@@ -972,14 +972,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly from 2010-01 to 2025-12, whole Thai system (EGAT, IPP, SPP and VSPP generation), EPPO Table 5.2-4 'Power Generation by Fuel (Detail)'. EPPO updates about two months after the month.</t>
+          <t>Monthly from 2010-01 to 2025-12, whole Thai system (EGAT, IPP, SPP and VSPP generation), EPPO Table 5.2-4 'Power Generation by Fuel (Detail)', extended with Table 5.2-2 for the current year. EPPO updates about two months after the month.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Files read this run: T05_02_04-1.xls (Last-Modified Mon, 14 Sep 2026 09:30:39 GMT); T05_02_05-1.xls (Last-Modified Mon, 14 Sep 2026 09:30:50 GMT); T05_02_05.xls (Last-Modified Mon, 14 Sep 2026 09:30:46 GMT)</t>
+          <t>Files read this run: T05_02_04-1.xls (Last-Modified Mon, 14 Sep 2026 09:30:39 GMT); T05_02_02.xls (Last-Modified Mon, 14 Sep 2026 09:30:04 GMT); T05_02_05-1.xls (Last-Modified Mon, 14 Sep 2026 09:30:50 GMT); T05_02_05.xls (Last-Modified Mon, 14 Sep 2026 09:30:46 GMT)</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I193"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3815,11 +3815,6 @@
           <t>Imports_MWh</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Lignite_MWh</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -3846,9 +3841,6 @@
       <c r="H2" t="n">
         <v>164141</v>
       </c>
-      <c r="I2" t="n">
-        <v>1516209</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -3875,9 +3867,6 @@
       <c r="H3" t="n">
         <v>143127</v>
       </c>
-      <c r="I3" t="n">
-        <v>1326957</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -3904,9 +3893,6 @@
       <c r="H4" t="n">
         <v>568333</v>
       </c>
-      <c r="I4" t="n">
-        <v>1562914</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -3933,9 +3919,6 @@
       <c r="H5" t="n">
         <v>741429</v>
       </c>
-      <c r="I5" t="n">
-        <v>1585884</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3962,9 +3945,6 @@
       <c r="H6" t="n">
         <v>791993</v>
       </c>
-      <c r="I6" t="n">
-        <v>1658240</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3991,9 +3971,6 @@
       <c r="H7" t="n">
         <v>789052</v>
       </c>
-      <c r="I7" t="n">
-        <v>1434946</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -4020,9 +3997,6 @@
       <c r="H8" t="n">
         <v>801080</v>
       </c>
-      <c r="I8" t="n">
-        <v>1436774</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -4049,9 +4023,6 @@
       <c r="H9" t="n">
         <v>768501</v>
       </c>
-      <c r="I9" t="n">
-        <v>1525457</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -4078,9 +4049,6 @@
       <c r="H10" t="n">
         <v>780247</v>
       </c>
-      <c r="I10" t="n">
-        <v>1363667</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -4107,9 +4075,6 @@
       <c r="H11" t="n">
         <v>795422</v>
       </c>
-      <c r="I11" t="n">
-        <v>1508242</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -4136,9 +4101,6 @@
       <c r="H12" t="n">
         <v>486988</v>
       </c>
-      <c r="I12" t="n">
-        <v>1525557</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4165,9 +4127,6 @@
       <c r="H13" t="n">
         <v>423471</v>
       </c>
-      <c r="I13" t="n">
-        <v>1542782</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4194,9 +4153,6 @@
       <c r="H14" t="n">
         <v>412365</v>
       </c>
-      <c r="I14" t="n">
-        <v>1692669</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4223,9 +4179,6 @@
       <c r="H15" t="n">
         <v>638013</v>
       </c>
-      <c r="I15" t="n">
-        <v>1493696</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4252,9 +4205,6 @@
       <c r="H16" t="n">
         <v>789541</v>
       </c>
-      <c r="I16" t="n">
-        <v>1579020</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -4281,9 +4231,6 @@
       <c r="H17" t="n">
         <v>1019115</v>
       </c>
-      <c r="I17" t="n">
-        <v>1623150</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -4310,9 +4257,6 @@
       <c r="H18" t="n">
         <v>1075411</v>
       </c>
-      <c r="I18" t="n">
-        <v>1710822</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -4339,9 +4283,6 @@
       <c r="H19" t="n">
         <v>1072215</v>
       </c>
-      <c r="I19" t="n">
-        <v>1616952</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -4368,9 +4309,6 @@
       <c r="H20" t="n">
         <v>1315343</v>
       </c>
-      <c r="I20" t="n">
-        <v>1703100</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -4397,9 +4335,6 @@
       <c r="H21" t="n">
         <v>792654</v>
       </c>
-      <c r="I21" t="n">
-        <v>1550255</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -4426,9 +4361,6 @@
       <c r="H22" t="n">
         <v>1120573</v>
       </c>
-      <c r="I22" t="n">
-        <v>1505429</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -4455,9 +4387,6 @@
       <c r="H23" t="n">
         <v>1164634</v>
       </c>
-      <c r="I23" t="n">
-        <v>1532098</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -4484,9 +4413,6 @@
       <c r="H24" t="n">
         <v>909586</v>
       </c>
-      <c r="I24" t="n">
-        <v>1346626</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -4513,9 +4439,6 @@
       <c r="H25" t="n">
         <v>464959</v>
       </c>
-      <c r="I25" t="n">
-        <v>1481809</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -4542,9 +4465,6 @@
       <c r="H26" t="n">
         <v>484490</v>
       </c>
-      <c r="I26" t="n">
-        <v>1599581</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -4571,9 +4491,6 @@
       <c r="H27" t="n">
         <v>799212</v>
       </c>
-      <c r="I27" t="n">
-        <v>1473982</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -4600,9 +4517,6 @@
       <c r="H28" t="n">
         <v>1163708</v>
       </c>
-      <c r="I28" t="n">
-        <v>1608576</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -4629,9 +4543,6 @@
       <c r="H29" t="n">
         <v>1135509</v>
       </c>
-      <c r="I29" t="n">
-        <v>1665710</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -4658,9 +4569,6 @@
       <c r="H30" t="n">
         <v>1076041</v>
       </c>
-      <c r="I30" t="n">
-        <v>1693856</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -4687,9 +4595,6 @@
       <c r="H31" t="n">
         <v>937377</v>
       </c>
-      <c r="I31" t="n">
-        <v>1608606</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -4716,9 +4621,6 @@
       <c r="H32" t="n">
         <v>946702</v>
       </c>
-      <c r="I32" t="n">
-        <v>1495184</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -4745,9 +4647,6 @@
       <c r="H33" t="n">
         <v>1114621</v>
       </c>
-      <c r="I33" t="n">
-        <v>1701825</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -4774,9 +4673,6 @@
       <c r="H34" t="n">
         <v>1140617</v>
       </c>
-      <c r="I34" t="n">
-        <v>1445580</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -4803,9 +4699,6 @@
       <c r="H35" t="n">
         <v>797106</v>
       </c>
-      <c r="I35" t="n">
-        <v>1457300</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -4832,9 +4725,6 @@
       <c r="H36" t="n">
         <v>519156</v>
       </c>
-      <c r="I36" t="n">
-        <v>1560391</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -4861,9 +4751,6 @@
       <c r="H37" t="n">
         <v>412887</v>
       </c>
-      <c r="I37" t="n">
-        <v>1491419</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -4890,9 +4777,6 @@
       <c r="H38" t="n">
         <v>362234</v>
       </c>
-      <c r="I38" t="n">
-        <v>1708802</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -4919,9 +4803,6 @@
       <c r="H39" t="n">
         <v>555799</v>
       </c>
-      <c r="I39" t="n">
-        <v>1529008</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -4948,9 +4829,6 @@
       <c r="H40" t="n">
         <v>818237</v>
       </c>
-      <c r="I40" t="n">
-        <v>1506018</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -4977,9 +4855,6 @@
       <c r="H41" t="n">
         <v>1140099</v>
       </c>
-      <c r="I41" t="n">
-        <v>1662799</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -5006,9 +4881,6 @@
       <c r="H42" t="n">
         <v>1310006</v>
       </c>
-      <c r="I42" t="n">
-        <v>1754149</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -5035,9 +4907,6 @@
       <c r="H43" t="n">
         <v>1268211</v>
       </c>
-      <c r="I43" t="n">
-        <v>1673957</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -5064,9 +4933,6 @@
       <c r="H44" t="n">
         <v>1297321</v>
       </c>
-      <c r="I44" t="n">
-        <v>1564109</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -5093,9 +4959,6 @@
       <c r="H45" t="n">
         <v>1515479</v>
       </c>
-      <c r="I45" t="n">
-        <v>1649180</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -5122,9 +4985,6 @@
       <c r="H46" t="n">
         <v>1596693</v>
       </c>
-      <c r="I46" t="n">
-        <v>1447167</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -5151,9 +5011,6 @@
       <c r="H47" t="n">
         <v>1341599</v>
       </c>
-      <c r="I47" t="n">
-        <v>1595547</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -5180,9 +5037,6 @@
       <c r="H48" t="n">
         <v>1044408</v>
       </c>
-      <c r="I48" t="n">
-        <v>1432643</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -5209,9 +5063,6 @@
       <c r="H49" t="n">
         <v>321704</v>
       </c>
-      <c r="I49" t="n">
-        <v>1574597</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -5238,9 +5089,6 @@
       <c r="H50" t="n">
         <v>591194</v>
       </c>
-      <c r="I50" t="n">
-        <v>1693689</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -5267,9 +5115,6 @@
       <c r="H51" t="n">
         <v>845460</v>
       </c>
-      <c r="I51" t="n">
-        <v>1394789</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -5296,9 +5141,6 @@
       <c r="H52" t="n">
         <v>1302479</v>
       </c>
-      <c r="I52" t="n">
-        <v>1645188</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -5325,9 +5167,6 @@
       <c r="H53" t="n">
         <v>1222559</v>
       </c>
-      <c r="I53" t="n">
-        <v>1664214</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -5354,9 +5193,6 @@
       <c r="H54" t="n">
         <v>1203938</v>
       </c>
-      <c r="I54" t="n">
-        <v>1731509</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -5383,9 +5219,6 @@
       <c r="H55" t="n">
         <v>1085918</v>
       </c>
-      <c r="I55" t="n">
-        <v>1682833</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -5412,9 +5245,6 @@
       <c r="H56" t="n">
         <v>1177907</v>
       </c>
-      <c r="I56" t="n">
-        <v>1617505</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -5441,9 +5271,6 @@
       <c r="H57" t="n">
         <v>1270629</v>
       </c>
-      <c r="I57" t="n">
-        <v>1569637</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -5470,9 +5297,6 @@
       <c r="H58" t="n">
         <v>1331876</v>
       </c>
-      <c r="I58" t="n">
-        <v>1512068</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -5499,9 +5323,6 @@
       <c r="H59" t="n">
         <v>1017368</v>
       </c>
-      <c r="I59" t="n">
-        <v>1620354</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -5528,9 +5349,6 @@
       <c r="H60" t="n">
         <v>717108</v>
       </c>
-      <c r="I60" t="n">
-        <v>1546181</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -5557,9 +5375,6 @@
       <c r="H61" t="n">
         <v>493277</v>
       </c>
-      <c r="I61" t="n">
-        <v>1692852</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -5586,9 +5401,6 @@
       <c r="H62" t="n">
         <v>355394</v>
       </c>
-      <c r="I62" t="n">
-        <v>1554090</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -5615,9 +5427,6 @@
       <c r="H63" t="n">
         <v>726002</v>
       </c>
-      <c r="I63" t="n">
-        <v>1275088</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -5644,9 +5453,6 @@
       <c r="H64" t="n">
         <v>1106605</v>
       </c>
-      <c r="I64" t="n">
-        <v>1349122</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -5673,9 +5479,6 @@
       <c r="H65" t="n">
         <v>1464628</v>
       </c>
-      <c r="I65" t="n">
-        <v>1367209</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -5702,9 +5505,6 @@
       <c r="H66" t="n">
         <v>1621936</v>
       </c>
-      <c r="I66" t="n">
-        <v>1471027</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -5731,9 +5531,6 @@
       <c r="H67" t="n">
         <v>1162287</v>
       </c>
-      <c r="I67" t="n">
-        <v>1472819</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -5760,9 +5557,6 @@
       <c r="H68" t="n">
         <v>758720</v>
       </c>
-      <c r="I68" t="n">
-        <v>1426224</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -5789,9 +5583,6 @@
       <c r="H69" t="n">
         <v>1373860</v>
       </c>
-      <c r="I69" t="n">
-        <v>1311616</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -5818,9 +5609,6 @@
       <c r="H70" t="n">
         <v>1634129</v>
       </c>
-      <c r="I70" t="n">
-        <v>1370493</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -5847,9 +5635,6 @@
       <c r="H71" t="n">
         <v>1668695</v>
       </c>
-      <c r="I71" t="n">
-        <v>1672232</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -5876,9 +5661,6 @@
       <c r="H72" t="n">
         <v>1395430</v>
       </c>
-      <c r="I72" t="n">
-        <v>1217798</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -5905,9 +5687,6 @@
       <c r="H73" t="n">
         <v>1146800</v>
       </c>
-      <c r="I73" t="n">
-        <v>1444586</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -5934,9 +5713,6 @@
       <c r="H74" t="n">
         <v>1147661</v>
       </c>
-      <c r="I74" t="n">
-        <v>1466677</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -5963,9 +5739,6 @@
       <c r="H75" t="n">
         <v>1096506</v>
       </c>
-      <c r="I75" t="n">
-        <v>1375566</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -5992,9 +5765,6 @@
       <c r="H76" t="n">
         <v>1339110</v>
       </c>
-      <c r="I76" t="n">
-        <v>1653559</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -6021,9 +5791,6 @@
       <c r="H77" t="n">
         <v>1394444</v>
       </c>
-      <c r="I77" t="n">
-        <v>1683833</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -6050,9 +5817,6 @@
       <c r="H78" t="n">
         <v>1910500</v>
       </c>
-      <c r="I78" t="n">
-        <v>1750298</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -6079,9 +5843,6 @@
       <c r="H79" t="n">
         <v>1701863</v>
       </c>
-      <c r="I79" t="n">
-        <v>1471412</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -6108,9 +5869,6 @@
       <c r="H80" t="n">
         <v>2098942</v>
       </c>
-      <c r="I80" t="n">
-        <v>1489506</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -6137,9 +5895,6 @@
       <c r="H81" t="n">
         <v>2251957</v>
       </c>
-      <c r="I81" t="n">
-        <v>1776855</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -6166,9 +5921,6 @@
       <c r="H82" t="n">
         <v>1553249</v>
       </c>
-      <c r="I82" t="n">
-        <v>1656068</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -6195,9 +5947,6 @@
       <c r="H83" t="n">
         <v>1943287</v>
       </c>
-      <c r="I83" t="n">
-        <v>1616876</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -6224,9 +5973,6 @@
       <c r="H84" t="n">
         <v>2146719</v>
       </c>
-      <c r="I84" t="n">
-        <v>1460310</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -6253,9 +5999,6 @@
       <c r="H85" t="n">
         <v>1241117</v>
       </c>
-      <c r="I85" t="n">
-        <v>1658468</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -6282,9 +6025,6 @@
       <c r="H86" t="n">
         <v>1162701</v>
       </c>
-      <c r="I86" t="n">
-        <v>1628835</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -6311,9 +6051,6 @@
       <c r="H87" t="n">
         <v>1445836</v>
       </c>
-      <c r="I87" t="n">
-        <v>1395078</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -6340,9 +6077,6 @@
       <c r="H88" t="n">
         <v>2128955</v>
       </c>
-      <c r="I88" t="n">
-        <v>1627992</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -6369,9 +6103,6 @@
       <c r="H89" t="n">
         <v>2223182</v>
       </c>
-      <c r="I89" t="n">
-        <v>1693264</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -6398,9 +6129,6 @@
       <c r="H90" t="n">
         <v>2174086</v>
       </c>
-      <c r="I90" t="n">
-        <v>1672040</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -6427,9 +6155,6 @@
       <c r="H91" t="n">
         <v>2231133</v>
       </c>
-      <c r="I91" t="n">
-        <v>1686196</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -6456,9 +6181,6 @@
       <c r="H92" t="n">
         <v>2415044</v>
       </c>
-      <c r="I92" t="n">
-        <v>1544369</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -6485,9 +6207,6 @@
       <c r="H93" t="n">
         <v>2198499</v>
       </c>
-      <c r="I93" t="n">
-        <v>1470435</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -6514,9 +6233,6 @@
       <c r="H94" t="n">
         <v>2509371</v>
       </c>
-      <c r="I94" t="n">
-        <v>1506457</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -6543,9 +6259,6 @@
       <c r="H95" t="n">
         <v>2079954</v>
       </c>
-      <c r="I95" t="n">
-        <v>1577040</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -6572,9 +6285,6 @@
       <c r="H96" t="n">
         <v>2048442</v>
       </c>
-      <c r="I96" t="n">
-        <v>1529329</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -6601,9 +6311,6 @@
       <c r="H97" t="n">
         <v>1810221</v>
       </c>
-      <c r="I97" t="n">
-        <v>1566743</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -6630,9 +6337,6 @@
       <c r="H98" t="n">
         <v>1862926</v>
       </c>
-      <c r="I98" t="n">
-        <v>1513191</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -6659,9 +6363,6 @@
       <c r="H99" t="n">
         <v>1734961</v>
       </c>
-      <c r="I99" t="n">
-        <v>1377156</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -6688,9 +6389,6 @@
       <c r="H100" t="n">
         <v>2228097</v>
       </c>
-      <c r="I100" t="n">
-        <v>1534222</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -6717,9 +6415,6 @@
       <c r="H101" t="n">
         <v>2055592</v>
       </c>
-      <c r="I101" t="n">
-        <v>1474844</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -6746,9 +6441,6 @@
       <c r="H102" t="n">
         <v>2259200</v>
       </c>
-      <c r="I102" t="n">
-        <v>1647915</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -6775,9 +6467,6 @@
       <c r="H103" t="n">
         <v>2149223</v>
       </c>
-      <c r="I103" t="n">
-        <v>1534349</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -6804,9 +6493,6 @@
       <c r="H104" t="n">
         <v>2220686</v>
       </c>
-      <c r="I104" t="n">
-        <v>1563816</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -6833,9 +6519,6 @@
       <c r="H105" t="n">
         <v>2535925</v>
       </c>
-      <c r="I105" t="n">
-        <v>1322583</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -6862,9 +6545,6 @@
       <c r="H106" t="n">
         <v>2801865</v>
       </c>
-      <c r="I106" t="n">
-        <v>1369958</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -6891,9 +6571,6 @@
       <c r="H107" t="n">
         <v>2677597</v>
       </c>
-      <c r="I107" t="n">
-        <v>1498700</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -6920,9 +6597,6 @@
       <c r="H108" t="n">
         <v>2201469</v>
       </c>
-      <c r="I108" t="n">
-        <v>1345168</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -6949,9 +6623,6 @@
       <c r="H109" t="n">
         <v>1941900</v>
       </c>
-      <c r="I109" t="n">
-        <v>1516535</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
@@ -6978,9 +6649,6 @@
       <c r="H110" t="n">
         <v>1736828</v>
       </c>
-      <c r="I110" t="n">
-        <v>1631406</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -7007,9 +6675,6 @@
       <c r="H111" t="n">
         <v>1843687</v>
       </c>
-      <c r="I111" t="n">
-        <v>1381928</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
@@ -7036,9 +6701,6 @@
       <c r="H112" t="n">
         <v>2184221</v>
       </c>
-      <c r="I112" t="n">
-        <v>1507964</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -7065,9 +6727,6 @@
       <c r="H113" t="n">
         <v>2045211</v>
       </c>
-      <c r="I113" t="n">
-        <v>1535337</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
@@ -7094,9 +6753,6 @@
       <c r="H114" t="n">
         <v>2039723</v>
       </c>
-      <c r="I114" t="n">
-        <v>1475549</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
@@ -7123,9 +6779,6 @@
       <c r="H115" t="n">
         <v>2066199</v>
       </c>
-      <c r="I115" t="n">
-        <v>1553305</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
@@ -7152,9 +6805,6 @@
       <c r="H116" t="n">
         <v>1975863</v>
       </c>
-      <c r="I116" t="n">
-        <v>1650278</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
@@ -7181,9 +6831,6 @@
       <c r="H117" t="n">
         <v>2939376</v>
       </c>
-      <c r="I117" t="n">
-        <v>1346019</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
@@ -7210,9 +6857,6 @@
       <c r="H118" t="n">
         <v>2683757</v>
       </c>
-      <c r="I118" t="n">
-        <v>1316210</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
@@ -7239,9 +6883,6 @@
       <c r="H119" t="n">
         <v>2417555</v>
       </c>
-      <c r="I119" t="n">
-        <v>1428677</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
@@ -7268,9 +6909,6 @@
       <c r="H120" t="n">
         <v>1539577</v>
       </c>
-      <c r="I120" t="n">
-        <v>1541462</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
@@ -7297,9 +6935,6 @@
       <c r="H121" t="n">
         <v>2074658</v>
       </c>
-      <c r="I121" t="n">
-        <v>1526744</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
@@ -7326,9 +6961,6 @@
       <c r="H122" t="n">
         <v>2002866</v>
       </c>
-      <c r="I122" t="n">
-        <v>1621449</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
@@ -7355,9 +6987,6 @@
       <c r="H123" t="n">
         <v>2005625</v>
       </c>
-      <c r="I123" t="n">
-        <v>1377242</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
@@ -7384,9 +7013,6 @@
       <c r="H124" t="n">
         <v>2321505</v>
       </c>
-      <c r="I124" t="n">
-        <v>1615669</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
@@ -7413,9 +7039,6 @@
       <c r="H125" t="n">
         <v>2132777</v>
       </c>
-      <c r="I125" t="n">
-        <v>1476831</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
@@ -7442,9 +7065,6 @@
       <c r="H126" t="n">
         <v>2229731</v>
       </c>
-      <c r="I126" t="n">
-        <v>1818025</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
@@ -7471,9 +7091,6 @@
       <c r="H127" t="n">
         <v>2189107</v>
       </c>
-      <c r="I127" t="n">
-        <v>1594870</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
@@ -7500,9 +7117,6 @@
       <c r="H128" t="n">
         <v>2088547</v>
       </c>
-      <c r="I128" t="n">
-        <v>1179849</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
@@ -7529,9 +7143,6 @@
       <c r="H129" t="n">
         <v>3341810</v>
       </c>
-      <c r="I129" t="n">
-        <v>1558975</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
@@ -7558,9 +7169,6 @@
       <c r="H130" t="n">
         <v>3283604</v>
       </c>
-      <c r="I130" t="n">
-        <v>1427763</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
@@ -7587,9 +7195,6 @@
       <c r="H131" t="n">
         <v>2983278</v>
       </c>
-      <c r="I131" t="n">
-        <v>1477888</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
@@ -7616,9 +7221,6 @@
       <c r="H132" t="n">
         <v>2515586</v>
       </c>
-      <c r="I132" t="n">
-        <v>1546584</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
@@ -7645,9 +7247,6 @@
       <c r="H133" t="n">
         <v>2456134</v>
       </c>
-      <c r="I133" t="n">
-        <v>1543398</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
@@ -7674,9 +7273,6 @@
       <c r="H134" t="n">
         <v>2043605</v>
       </c>
-      <c r="I134" t="n">
-        <v>1771348</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
@@ -7703,9 +7299,6 @@
       <c r="H135" t="n">
         <v>1769580</v>
       </c>
-      <c r="I135" t="n">
-        <v>1483507</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
@@ -7732,9 +7325,6 @@
       <c r="H136" t="n">
         <v>2690819</v>
       </c>
-      <c r="I136" t="n">
-        <v>1562103</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n">
@@ -7761,9 +7351,6 @@
       <c r="H137" t="n">
         <v>2567607</v>
       </c>
-      <c r="I137" t="n">
-        <v>1550109</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n">
@@ -7790,9 +7377,6 @@
       <c r="H138" t="n">
         <v>2824509</v>
       </c>
-      <c r="I138" t="n">
-        <v>1662665</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
@@ -7819,9 +7403,6 @@
       <c r="H139" t="n">
         <v>3191182</v>
       </c>
-      <c r="I139" t="n">
-        <v>1615041</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
@@ -7848,9 +7429,6 @@
       <c r="H140" t="n">
         <v>3374964</v>
       </c>
-      <c r="I140" t="n">
-        <v>1769799</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
@@ -7877,9 +7455,6 @@
       <c r="H141" t="n">
         <v>3742936</v>
       </c>
-      <c r="I141" t="n">
-        <v>1785466</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
@@ -7906,9 +7481,6 @@
       <c r="H142" t="n">
         <v>3374003</v>
       </c>
-      <c r="I142" t="n">
-        <v>1491482</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n">
@@ -7935,9 +7507,6 @@
       <c r="H143" t="n">
         <v>2850703</v>
       </c>
-      <c r="I143" t="n">
-        <v>1631107</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n">
@@ -7964,9 +7533,6 @@
       <c r="H144" t="n">
         <v>2465338</v>
       </c>
-      <c r="I144" t="n">
-        <v>1674530</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
@@ -7993,9 +7559,6 @@
       <c r="H145" t="n">
         <v>2461042</v>
       </c>
-      <c r="I145" t="n">
-        <v>1529636</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n">
@@ -8022,9 +7585,6 @@
       <c r="H146" t="n">
         <v>2293780</v>
       </c>
-      <c r="I146" t="n">
-        <v>1611349</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
@@ -8051,9 +7611,6 @@
       <c r="H147" t="n">
         <v>1905475</v>
       </c>
-      <c r="I147" t="n">
-        <v>1484300</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n">
@@ -8080,9 +7637,6 @@
       <c r="H148" t="n">
         <v>2936540</v>
       </c>
-      <c r="I148" t="n">
-        <v>1363712</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n">
@@ -8109,9 +7663,6 @@
       <c r="H149" t="n">
         <v>2878973</v>
       </c>
-      <c r="I149" t="n">
-        <v>1457452</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
@@ -8138,9 +7689,6 @@
       <c r="H150" t="n">
         <v>3223064</v>
       </c>
-      <c r="I150" t="n">
-        <v>1729646</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
@@ -8167,9 +7715,6 @@
       <c r="H151" t="n">
         <v>3460838</v>
       </c>
-      <c r="I151" t="n">
-        <v>1480059</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
@@ -8196,9 +7741,6 @@
       <c r="H152" t="n">
         <v>3878508</v>
       </c>
-      <c r="I152" t="n">
-        <v>1574808</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
@@ -8225,9 +7767,6 @@
       <c r="H153" t="n">
         <v>3872273</v>
       </c>
-      <c r="I153" t="n">
-        <v>1730317</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n">
@@ -8254,9 +7793,6 @@
       <c r="H154" t="n">
         <v>3416562</v>
       </c>
-      <c r="I154" t="n">
-        <v>1503939</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
@@ -8283,9 +7819,6 @@
       <c r="H155" t="n">
         <v>3144125</v>
       </c>
-      <c r="I155" t="n">
-        <v>1589835</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
@@ -8312,9 +7845,6 @@
       <c r="H156" t="n">
         <v>2088742</v>
       </c>
-      <c r="I156" t="n">
-        <v>1591351</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
@@ -8341,9 +7871,6 @@
       <c r="H157" t="n">
         <v>2372876</v>
       </c>
-      <c r="I157" t="n">
-        <v>1631655</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n">
@@ -8370,9 +7897,6 @@
       <c r="H158" t="n">
         <v>2307077</v>
       </c>
-      <c r="I158" t="n">
-        <v>1542833</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -8399,9 +7923,6 @@
       <c r="H159" t="n">
         <v>1984746</v>
       </c>
-      <c r="I159" t="n">
-        <v>1384372</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n">
@@ -8428,9 +7949,6 @@
       <c r="H160" t="n">
         <v>2535453</v>
       </c>
-      <c r="I160" t="n">
-        <v>1453997</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
@@ -8457,9 +7975,6 @@
       <c r="H161" t="n">
         <v>2310630</v>
       </c>
-      <c r="I161" t="n">
-        <v>1567241</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n">
@@ -8486,9 +8001,6 @@
       <c r="H162" t="n">
         <v>2530190</v>
       </c>
-      <c r="I162" t="n">
-        <v>1500054</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
@@ -8515,9 +8027,6 @@
       <c r="H163" t="n">
         <v>2388136</v>
       </c>
-      <c r="I163" t="n">
-        <v>1593967</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n">
@@ -8544,9 +8053,6 @@
       <c r="H164" t="n">
         <v>2697208</v>
       </c>
-      <c r="I164" t="n">
-        <v>1399440</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
@@ -8573,9 +8079,6 @@
       <c r="H165" t="n">
         <v>3299362</v>
       </c>
-      <c r="I165" t="n">
-        <v>1275298</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n">
@@ -8602,9 +8105,6 @@
       <c r="H166" t="n">
         <v>3741591</v>
       </c>
-      <c r="I166" t="n">
-        <v>1562945</v>
-      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
@@ -8631,9 +8131,6 @@
       <c r="H167" t="n">
         <v>3663124</v>
       </c>
-      <c r="I167" t="n">
-        <v>1420210</v>
-      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n">
@@ -8660,9 +8157,6 @@
       <c r="H168" t="n">
         <v>2550601</v>
       </c>
-      <c r="I168" t="n">
-        <v>1457825</v>
-      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
@@ -8689,9 +8183,6 @@
       <c r="H169" t="n">
         <v>2797034</v>
       </c>
-      <c r="I169" t="n">
-        <v>1302054</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n">
@@ -8718,9 +8209,6 @@
       <c r="H170" t="n">
         <v>2143292</v>
       </c>
-      <c r="I170" t="n">
-        <v>1391178</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
@@ -8747,9 +8235,6 @@
       <c r="H171" t="n">
         <v>2050547</v>
       </c>
-      <c r="I171" t="n">
-        <v>1501359</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
@@ -8776,9 +8261,6 @@
       <c r="H172" t="n">
         <v>2687751</v>
       </c>
-      <c r="I172" t="n">
-        <v>1452684</v>
-      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
@@ -8805,9 +8287,6 @@
       <c r="H173" t="n">
         <v>2854629</v>
       </c>
-      <c r="I173" t="n">
-        <v>1386307</v>
-      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n">
@@ -8834,9 +8313,6 @@
       <c r="H174" t="n">
         <v>2691007</v>
       </c>
-      <c r="I174" t="n">
-        <v>1468749</v>
-      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
@@ -8863,9 +8339,6 @@
       <c r="H175" t="n">
         <v>2853091</v>
       </c>
-      <c r="I175" t="n">
-        <v>1394129</v>
-      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n">
@@ -8892,9 +8365,6 @@
       <c r="H176" t="n">
         <v>3804053</v>
       </c>
-      <c r="I176" t="n">
-        <v>1416156</v>
-      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n">
@@ -8921,9 +8391,6 @@
       <c r="H177" t="n">
         <v>3524402</v>
       </c>
-      <c r="I177" t="n">
-        <v>1172600</v>
-      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n">
@@ -8950,9 +8417,6 @@
       <c r="H178" t="n">
         <v>3959712</v>
       </c>
-      <c r="I178" t="n">
-        <v>1408260</v>
-      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n">
@@ -8979,9 +8443,6 @@
       <c r="H179" t="n">
         <v>4025897</v>
       </c>
-      <c r="I179" t="n">
-        <v>1574027</v>
-      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n">
@@ -9008,9 +8469,6 @@
       <c r="H180" t="n">
         <v>2824822</v>
       </c>
-      <c r="I180" t="n">
-        <v>1451226</v>
-      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n">
@@ -9037,9 +8495,6 @@
       <c r="H181" t="n">
         <v>2565840</v>
       </c>
-      <c r="I181" t="n">
-        <v>1612357</v>
-      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n">
@@ -9066,9 +8521,6 @@
       <c r="H182" t="n">
         <v>2215532</v>
       </c>
-      <c r="I182" t="n">
-        <v>1436106</v>
-      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n">
@@ -9095,9 +8547,6 @@
       <c r="H183" t="n">
         <v>1929714</v>
       </c>
-      <c r="I183" t="n">
-        <v>1467056</v>
-      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="n">
@@ -9124,9 +8573,6 @@
       <c r="H184" t="n">
         <v>3001011</v>
       </c>
-      <c r="I184" t="n">
-        <v>1661581</v>
-      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n">
@@ -9153,9 +8599,6 @@
       <c r="H185" t="n">
         <v>2806938</v>
       </c>
-      <c r="I185" t="n">
-        <v>1200487</v>
-      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="n">
@@ -9182,9 +8625,6 @@
       <c r="H186" t="n">
         <v>3252124</v>
       </c>
-      <c r="I186" t="n">
-        <v>1551979</v>
-      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
@@ -9211,9 +8651,6 @@
       <c r="H187" t="n">
         <v>3596648</v>
       </c>
-      <c r="I187" t="n">
-        <v>1664040</v>
-      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n">
@@ -9240,9 +8677,6 @@
       <c r="H188" t="n">
         <v>3913353</v>
       </c>
-      <c r="I188" t="n">
-        <v>1568072</v>
-      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n">
@@ -9269,9 +8703,6 @@
       <c r="H189" t="n">
         <v>4390294</v>
       </c>
-      <c r="I189" t="n">
-        <v>1620497</v>
-      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="n">
@@ -9298,9 +8729,6 @@
       <c r="H190" t="n">
         <v>4455080</v>
       </c>
-      <c r="I190" t="n">
-        <v>1585858</v>
-      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
@@ -9327,9 +8755,6 @@
       <c r="H191" t="n">
         <v>4052188</v>
       </c>
-      <c r="I191" t="n">
-        <v>1546646</v>
-      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n">
@@ -9356,9 +8781,6 @@
       <c r="H192" t="n">
         <v>3073963</v>
       </c>
-      <c r="I192" t="n">
-        <v>1106020</v>
-      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n">
@@ -9384,9 +8806,6 @@
       </c>
       <c r="H193" t="n">
         <v>2449029</v>
-      </c>
-      <c r="I193" t="n">
-        <v>639800</v>
       </c>
     </row>
   </sheetData>
@@ -9400,7 +8819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D205"/>
+  <dimension ref="A1:D200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12211,31 +11630,6 @@
         <v>80.28088793298717</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="4" t="n">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="4" t="n">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="4" t="n">
-        <v>46296</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="4" t="n">
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="4" t="n">
-        <v>46357</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
@@ -157,7 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Thailand power generation by fuel (EPPO, whole system) (to Dec/25)</a:t>
+              <a:t>Thailand power generation by fuel (EPPO, whole system) (to Jul/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -187,12 +187,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$61</f>
+              <f>'Chart'!$B$2:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -215,12 +215,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$61</f>
+              <f>'Chart'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$61</f>
+              <f>'Chart'!$D$2:$D$68</f>
             </numRef>
           </val>
         </ser>
@@ -271,12 +271,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$61</f>
+              <f>'Chart'!$E$2:$E$68</f>
             </numRef>
           </val>
         </ser>
@@ -299,12 +299,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$61</f>
+              <f>'Chart'!$F$2:$F$68</f>
             </numRef>
           </val>
         </ser>
@@ -327,12 +327,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$61</f>
+              <f>'Chart'!$G$2:$G$68</f>
             </numRef>
           </val>
         </ser>
@@ -355,12 +355,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$61</f>
+              <f>'Chart'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$61</f>
+              <f>'Chart'!$H$2:$H$68</f>
             </numRef>
           </val>
         </ser>
@@ -972,7 +972,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly from 2010-01 to 2025-12, whole Thai system (EGAT, IPP, SPP and VSPP generation), EPPO Table 5.2-4 'Power Generation by Fuel (Detail)', extended with Table 5.2-2 for the current year. EPPO updates about two months after the month.</t>
+          <t>Monthly from 2010-01 to 2026-07, whole Thai system (EGAT, IPP, SPP and VSPP generation), EPPO Table 5.2-4 'Power Generation by Fuel (Detail)', extended with Table 5.2-2 for the current year. EPPO updates about two months after the month.</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2310,10 +2310,10 @@
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>787.34</v>
+        <v>4.771</v>
       </c>
       <c r="C50" t="n">
-        <v>9140.709000000001</v>
+        <v>55.387</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2322,13 +2322,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>2051.257</v>
+        <v>12.429</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2308.509</v>
+        <v>13.988</v>
       </c>
     </row>
     <row r="51">
@@ -2336,10 +2336,10 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>727.822</v>
+        <v>4.249</v>
       </c>
       <c r="C51" t="n">
-        <v>9756.023999999999</v>
+        <v>56.95</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2348,13 +2348,13 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>2762.693</v>
+        <v>16.127</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1954.756</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="52">
@@ -2362,10 +2362,10 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>697.0309999999999</v>
+        <v>3.377</v>
       </c>
       <c r="C52" t="n">
-        <v>11530.851</v>
+        <v>55.872</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2374,13 +2374,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>3183.313</v>
+        <v>15.425</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2225.814</v>
+        <v>10.785</v>
       </c>
     </row>
     <row r="53">
@@ -2388,10 +2388,10 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>655.7</v>
+        <v>3.294</v>
       </c>
       <c r="C53" t="n">
-        <v>11877.54</v>
+        <v>59.662</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2400,13 +2400,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>2551.106</v>
+        <v>12.814</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2016.707</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="54">
@@ -2414,10 +2414,10 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>627.136</v>
+        <v>3.072</v>
       </c>
       <c r="C54" t="n">
-        <v>11604.01</v>
+        <v>56.835</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2426,13 +2426,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>3067.699</v>
+        <v>15.025</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1866.186</v>
+        <v>9.141</v>
       </c>
     </row>
     <row r="55">
@@ -2440,10 +2440,10 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>504.016</v>
+        <v>2.578</v>
       </c>
       <c r="C55" t="n">
-        <v>10362.877</v>
+        <v>53.015</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>3122.305</v>
+        <v>15.973</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1961.117</v>
+        <v>10.033</v>
       </c>
     </row>
     <row r="56">
@@ -2466,10 +2466,10 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>445.793</v>
+        <v>2.256</v>
       </c>
       <c r="C56" t="n">
-        <v>10214.604</v>
+        <v>51.684</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>3034.877</v>
+        <v>15.356</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2154.822</v>
+        <v>10.903</v>
       </c>
     </row>
     <row r="57">
@@ -2492,10 +2492,10 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>703.032</v>
+        <v>3.498</v>
       </c>
       <c r="C57" t="n">
-        <v>9900.312</v>
+        <v>49.261</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2504,13 +2504,13 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>3118.889</v>
+        <v>15.519</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1985.117</v>
+        <v>9.878</v>
       </c>
     </row>
     <row r="58">
@@ -2518,10 +2518,10 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>493.093</v>
+        <v>2.585</v>
       </c>
       <c r="C58" t="n">
-        <v>9427.883</v>
+        <v>49.425</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2530,13 +2530,13 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>3037.919</v>
+        <v>15.926</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1661.199</v>
+        <v>8.709000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2544,10 +2544,10 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>567.329</v>
+        <v>2.918</v>
       </c>
       <c r="C59" t="n">
-        <v>10120.218</v>
+        <v>52.055</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2556,13 +2556,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>2998.377</v>
+        <v>15.423</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1703.297</v>
+        <v>8.760999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2570,10 +2570,10 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>654.2140000000001</v>
+        <v>3.777</v>
       </c>
       <c r="C60" t="n">
-        <v>9276.867</v>
+        <v>53.562</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -2582,13 +2582,13 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>2525.209</v>
+        <v>14.58</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1789.464</v>
+        <v>10.332</v>
       </c>
     </row>
     <row r="61">
@@ -2596,10 +2596,10 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>756.461</v>
+        <v>4.302</v>
       </c>
       <c r="C61" t="n">
-        <v>10122.495</v>
+        <v>57.572</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -2608,13 +2608,195 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>2125.153</v>
+        <v>12.087</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2129.055</v>
+        <v>12.11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5.394</v>
+      </c>
+      <c r="C62" t="n">
+        <v>59.056</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6.683</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>13.251</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B63" t="n">
+        <v>5.037</v>
+      </c>
+      <c r="C63" t="n">
+        <v>63.114</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8.082000000000001</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>10.925</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B64" t="n">
+        <v>5.487</v>
+      </c>
+      <c r="C64" t="n">
+        <v>59.155</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>9.076000000000001</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>10.98</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="C65" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>10.466</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>9.965999999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="C66" t="n">
+        <v>61.331</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>10.344</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>9.177999999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>2.909</v>
+      </c>
+      <c r="C67" t="n">
+        <v>61.616</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>10.309</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>10.102</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2.891</v>
+      </c>
+      <c r="C68" t="n">
+        <v>56.913</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>10.297</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>10.768</v>
       </c>
     </row>
   </sheetData>
@@ -3771,7 +3953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8501,25 +8683,25 @@
         <v>45658</v>
       </c>
       <c r="B182" t="n">
-        <v>787340</v>
+        <v>4771</v>
       </c>
       <c r="C182" t="n">
-        <v>9140709</v>
+        <v>55387</v>
       </c>
       <c r="D182" t="n">
-        <v>2051257</v>
+        <v>12429</v>
       </c>
       <c r="E182" t="n">
-        <v>1492</v>
+        <v>9</v>
       </c>
       <c r="F182" t="n">
-        <v>2307017</v>
+        <v>13979</v>
       </c>
       <c r="G182" t="n">
-        <v>14287815</v>
+        <v>86575</v>
       </c>
       <c r="H182" t="n">
-        <v>2215532</v>
+        <v>13425</v>
       </c>
     </row>
     <row r="183">
@@ -8527,25 +8709,25 @@
         <v>45689</v>
       </c>
       <c r="B183" t="n">
-        <v>727822</v>
+        <v>4249</v>
       </c>
       <c r="C183" t="n">
-        <v>9756024</v>
+        <v>56950</v>
       </c>
       <c r="D183" t="n">
-        <v>2762693</v>
+        <v>16127</v>
       </c>
       <c r="E183" t="n">
-        <v>6423</v>
+        <v>37</v>
       </c>
       <c r="F183" t="n">
-        <v>1948333</v>
+        <v>11373</v>
       </c>
       <c r="G183" t="n">
-        <v>15201295</v>
+        <v>88736</v>
       </c>
       <c r="H183" t="n">
-        <v>1929714</v>
+        <v>11264</v>
       </c>
     </row>
     <row r="184">
@@ -8553,25 +8735,25 @@
         <v>45717</v>
       </c>
       <c r="B184" t="n">
-        <v>697031</v>
+        <v>3377</v>
       </c>
       <c r="C184" t="n">
-        <v>11530851</v>
+        <v>55872</v>
       </c>
       <c r="D184" t="n">
-        <v>3183313</v>
+        <v>15425</v>
       </c>
       <c r="E184" t="n">
-        <v>2325</v>
+        <v>11</v>
       </c>
       <c r="F184" t="n">
-        <v>2223489</v>
+        <v>10774</v>
       </c>
       <c r="G184" t="n">
-        <v>17637010</v>
+        <v>85459</v>
       </c>
       <c r="H184" t="n">
-        <v>3001011</v>
+        <v>14541</v>
       </c>
     </row>
     <row r="185">
@@ -8579,25 +8761,25 @@
         <v>45748</v>
       </c>
       <c r="B185" t="n">
-        <v>655700</v>
+        <v>3294</v>
       </c>
       <c r="C185" t="n">
-        <v>11877540</v>
+        <v>59662</v>
       </c>
       <c r="D185" t="n">
-        <v>2551106</v>
+        <v>12814</v>
       </c>
       <c r="E185" t="n">
-        <v>2849</v>
+        <v>14</v>
       </c>
       <c r="F185" t="n">
-        <v>2013858</v>
+        <v>10116</v>
       </c>
       <c r="G185" t="n">
-        <v>17101053</v>
+        <v>85900</v>
       </c>
       <c r="H185" t="n">
-        <v>2806938</v>
+        <v>14100</v>
       </c>
     </row>
     <row r="186">
@@ -8605,25 +8787,25 @@
         <v>45778</v>
       </c>
       <c r="B186" t="n">
-        <v>627136</v>
+        <v>3072</v>
       </c>
       <c r="C186" t="n">
-        <v>11604010</v>
+        <v>56835</v>
       </c>
       <c r="D186" t="n">
-        <v>3067699</v>
+        <v>15025</v>
       </c>
       <c r="E186" t="n">
-        <v>2594</v>
+        <v>13</v>
       </c>
       <c r="F186" t="n">
-        <v>1863592</v>
+        <v>9128</v>
       </c>
       <c r="G186" t="n">
-        <v>17165031</v>
+        <v>84072</v>
       </c>
       <c r="H186" t="n">
-        <v>3252124</v>
+        <v>15928</v>
       </c>
     </row>
     <row r="187">
@@ -8631,25 +8813,25 @@
         <v>45809</v>
       </c>
       <c r="B187" t="n">
-        <v>504016</v>
+        <v>2578</v>
       </c>
       <c r="C187" t="n">
-        <v>10362877</v>
+        <v>53015</v>
       </c>
       <c r="D187" t="n">
-        <v>3122305</v>
+        <v>15973</v>
       </c>
       <c r="E187" t="n">
-        <v>1591</v>
+        <v>8</v>
       </c>
       <c r="F187" t="n">
-        <v>1959526</v>
+        <v>10025</v>
       </c>
       <c r="G187" t="n">
-        <v>15950316</v>
+        <v>81600</v>
       </c>
       <c r="H187" t="n">
-        <v>3596648</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="188">
@@ -8657,25 +8839,25 @@
         <v>45839</v>
       </c>
       <c r="B188" t="n">
-        <v>445793</v>
+        <v>2256</v>
       </c>
       <c r="C188" t="n">
-        <v>10214604</v>
+        <v>51684</v>
       </c>
       <c r="D188" t="n">
-        <v>3034877</v>
+        <v>15356</v>
       </c>
       <c r="E188" t="n">
-        <v>5164</v>
+        <v>26</v>
       </c>
       <c r="F188" t="n">
-        <v>2149658</v>
+        <v>10877</v>
       </c>
       <c r="G188" t="n">
-        <v>15850096</v>
+        <v>80199</v>
       </c>
       <c r="H188" t="n">
-        <v>3913353</v>
+        <v>19801</v>
       </c>
     </row>
     <row r="189">
@@ -8683,25 +8865,25 @@
         <v>45870</v>
       </c>
       <c r="B189" t="n">
-        <v>703032</v>
+        <v>3498</v>
       </c>
       <c r="C189" t="n">
-        <v>9900312</v>
+        <v>49261</v>
       </c>
       <c r="D189" t="n">
-        <v>3118889</v>
+        <v>15519</v>
       </c>
       <c r="E189" t="n">
-        <v>2336</v>
+        <v>12</v>
       </c>
       <c r="F189" t="n">
-        <v>1982781</v>
+        <v>9866</v>
       </c>
       <c r="G189" t="n">
-        <v>15707349</v>
+        <v>78155</v>
       </c>
       <c r="H189" t="n">
-        <v>4390294</v>
+        <v>21845</v>
       </c>
     </row>
     <row r="190">
@@ -8709,25 +8891,25 @@
         <v>45901</v>
       </c>
       <c r="B190" t="n">
-        <v>493093</v>
+        <v>2585</v>
       </c>
       <c r="C190" t="n">
-        <v>9427883</v>
+        <v>49425</v>
       </c>
       <c r="D190" t="n">
-        <v>3037919</v>
+        <v>15926</v>
       </c>
       <c r="E190" t="n">
-        <v>3387</v>
+        <v>18</v>
       </c>
       <c r="F190" t="n">
-        <v>1657812</v>
+        <v>8691</v>
       </c>
       <c r="G190" t="n">
-        <v>14620093</v>
+        <v>76645</v>
       </c>
       <c r="H190" t="n">
-        <v>4455080</v>
+        <v>23355</v>
       </c>
     </row>
     <row r="191">
@@ -8735,25 +8917,25 @@
         <v>45931</v>
       </c>
       <c r="B191" t="n">
-        <v>567329</v>
+        <v>2918</v>
       </c>
       <c r="C191" t="n">
-        <v>10120218</v>
+        <v>52055</v>
       </c>
       <c r="D191" t="n">
-        <v>2998377</v>
+        <v>15423</v>
       </c>
       <c r="E191" t="n">
-        <v>3890</v>
+        <v>20</v>
       </c>
       <c r="F191" t="n">
-        <v>1699407</v>
+        <v>8741</v>
       </c>
       <c r="G191" t="n">
-        <v>15389221</v>
+        <v>79157</v>
       </c>
       <c r="H191" t="n">
-        <v>4052188</v>
+        <v>20843</v>
       </c>
     </row>
     <row r="192">
@@ -8761,25 +8943,25 @@
         <v>45962</v>
       </c>
       <c r="B192" t="n">
-        <v>654214</v>
+        <v>3777</v>
       </c>
       <c r="C192" t="n">
-        <v>9276867</v>
+        <v>53562</v>
       </c>
       <c r="D192" t="n">
-        <v>2525209</v>
+        <v>14580</v>
       </c>
       <c r="E192" t="n">
-        <v>18089</v>
+        <v>104</v>
       </c>
       <c r="F192" t="n">
-        <v>1771375</v>
+        <v>10228</v>
       </c>
       <c r="G192" t="n">
-        <v>14245755</v>
+        <v>82252</v>
       </c>
       <c r="H192" t="n">
-        <v>3073963</v>
+        <v>17748</v>
       </c>
     </row>
     <row r="193">
@@ -8787,25 +8969,207 @@
         <v>45992</v>
       </c>
       <c r="B193" t="n">
-        <v>756461</v>
+        <v>4302</v>
       </c>
       <c r="C193" t="n">
-        <v>10122495</v>
+        <v>57572</v>
       </c>
       <c r="D193" t="n">
-        <v>2125153</v>
+        <v>12087</v>
       </c>
       <c r="E193" t="n">
-        <v>83081</v>
+        <v>473</v>
       </c>
       <c r="F193" t="n">
-        <v>2045974</v>
+        <v>11637</v>
       </c>
       <c r="G193" t="n">
-        <v>15133164</v>
+        <v>86071</v>
       </c>
       <c r="H193" t="n">
-        <v>2449029</v>
+        <v>13929</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B194" t="n">
+        <v>5394</v>
+      </c>
+      <c r="C194" t="n">
+        <v>59056</v>
+      </c>
+      <c r="D194" t="n">
+        <v>6683</v>
+      </c>
+      <c r="E194" t="n">
+        <v>264</v>
+      </c>
+      <c r="F194" t="n">
+        <v>12987</v>
+      </c>
+      <c r="G194" t="n">
+        <v>84384</v>
+      </c>
+      <c r="H194" t="n">
+        <v>15616</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B195" t="n">
+        <v>5037</v>
+      </c>
+      <c r="C195" t="n">
+        <v>63114</v>
+      </c>
+      <c r="D195" t="n">
+        <v>8082</v>
+      </c>
+      <c r="E195" t="n">
+        <v>4</v>
+      </c>
+      <c r="F195" t="n">
+        <v>10921</v>
+      </c>
+      <c r="G195" t="n">
+        <v>87158</v>
+      </c>
+      <c r="H195" t="n">
+        <v>12842</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B196" t="n">
+        <v>5487</v>
+      </c>
+      <c r="C196" t="n">
+        <v>59155</v>
+      </c>
+      <c r="D196" t="n">
+        <v>9076</v>
+      </c>
+      <c r="E196" t="n">
+        <v>6</v>
+      </c>
+      <c r="F196" t="n">
+        <v>10974</v>
+      </c>
+      <c r="G196" t="n">
+        <v>84699</v>
+      </c>
+      <c r="H196" t="n">
+        <v>15301</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B197" t="n">
+        <v>4489</v>
+      </c>
+      <c r="C197" t="n">
+        <v>61430</v>
+      </c>
+      <c r="D197" t="n">
+        <v>10466</v>
+      </c>
+      <c r="E197" t="n">
+        <v>10</v>
+      </c>
+      <c r="F197" t="n">
+        <v>9956</v>
+      </c>
+      <c r="G197" t="n">
+        <v>86351</v>
+      </c>
+      <c r="H197" t="n">
+        <v>13649</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B198" t="n">
+        <v>3478</v>
+      </c>
+      <c r="C198" t="n">
+        <v>61331</v>
+      </c>
+      <c r="D198" t="n">
+        <v>10344</v>
+      </c>
+      <c r="E198" t="n">
+        <v>13</v>
+      </c>
+      <c r="F198" t="n">
+        <v>9165</v>
+      </c>
+      <c r="G198" t="n">
+        <v>84331</v>
+      </c>
+      <c r="H198" t="n">
+        <v>15669</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B199" t="n">
+        <v>2909</v>
+      </c>
+      <c r="C199" t="n">
+        <v>61616</v>
+      </c>
+      <c r="D199" t="n">
+        <v>10309</v>
+      </c>
+      <c r="E199" t="n">
+        <v>30</v>
+      </c>
+      <c r="F199" t="n">
+        <v>10072</v>
+      </c>
+      <c r="G199" t="n">
+        <v>84937</v>
+      </c>
+      <c r="H199" t="n">
+        <v>15063</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2891</v>
+      </c>
+      <c r="C200" t="n">
+        <v>56913</v>
+      </c>
+      <c r="D200" t="n">
+        <v>10297</v>
+      </c>
+      <c r="E200" t="n">
+        <v>123</v>
+      </c>
+      <c r="F200" t="n">
+        <v>10645</v>
+      </c>
+      <c r="G200" t="n">
+        <v>80869</v>
+      </c>
+      <c r="H200" t="n">
+        <v>19131</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
@@ -2310,10 +2310,10 @@
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>4.771</v>
+        <v>787.34</v>
       </c>
       <c r="C50" t="n">
-        <v>55.387</v>
+        <v>9140.709000000001</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2322,13 +2322,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>12.429</v>
+        <v>2051.257</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>13.988</v>
+        <v>2308.509</v>
       </c>
     </row>
     <row r="51">
@@ -2336,10 +2336,10 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>4.249</v>
+        <v>727.822</v>
       </c>
       <c r="C51" t="n">
-        <v>56.95</v>
+        <v>9756.023999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2348,13 +2348,13 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>16.127</v>
+        <v>2762.693</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>11.41</v>
+        <v>1954.756</v>
       </c>
     </row>
     <row r="52">
@@ -2362,10 +2362,10 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>3.377</v>
+        <v>697.0309999999999</v>
       </c>
       <c r="C52" t="n">
-        <v>55.872</v>
+        <v>11530.851</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2374,13 +2374,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>15.425</v>
+        <v>3183.313</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>10.785</v>
+        <v>2225.814</v>
       </c>
     </row>
     <row r="53">
@@ -2388,10 +2388,10 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>3.294</v>
+        <v>655.7</v>
       </c>
       <c r="C53" t="n">
-        <v>59.662</v>
+        <v>11877.54</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2400,13 +2400,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>12.814</v>
+        <v>2551.106</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>10.13</v>
+        <v>2016.707</v>
       </c>
     </row>
     <row r="54">
@@ -2414,10 +2414,10 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>3.072</v>
+        <v>627.136</v>
       </c>
       <c r="C54" t="n">
-        <v>56.835</v>
+        <v>11604.01</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2426,13 +2426,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>15.025</v>
+        <v>3067.699</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>9.141</v>
+        <v>1866.186</v>
       </c>
     </row>
     <row r="55">
@@ -2440,10 +2440,10 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>2.578</v>
+        <v>504.016</v>
       </c>
       <c r="C55" t="n">
-        <v>53.015</v>
+        <v>10362.877</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>15.973</v>
+        <v>3122.305</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>10.033</v>
+        <v>1961.117</v>
       </c>
     </row>
     <row r="56">
@@ -2466,10 +2466,10 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>2.256</v>
+        <v>445.793</v>
       </c>
       <c r="C56" t="n">
-        <v>51.684</v>
+        <v>10214.604</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>15.356</v>
+        <v>3034.877</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>10.903</v>
+        <v>2154.822</v>
       </c>
     </row>
     <row r="57">
@@ -2492,10 +2492,10 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>3.498</v>
+        <v>703.032</v>
       </c>
       <c r="C57" t="n">
-        <v>49.261</v>
+        <v>9900.312</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2504,13 +2504,13 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>15.519</v>
+        <v>3118.889</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>9.878</v>
+        <v>1985.117</v>
       </c>
     </row>
     <row r="58">
@@ -2518,10 +2518,10 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>2.585</v>
+        <v>493.093</v>
       </c>
       <c r="C58" t="n">
-        <v>49.425</v>
+        <v>9427.883</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2530,13 +2530,13 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>15.926</v>
+        <v>3037.919</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>8.709000000000001</v>
+        <v>1661.199</v>
       </c>
     </row>
     <row r="59">
@@ -2544,10 +2544,10 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>2.918</v>
+        <v>567.329</v>
       </c>
       <c r="C59" t="n">
-        <v>52.055</v>
+        <v>10120.218</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2556,13 +2556,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>15.423</v>
+        <v>2998.377</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>8.760999999999999</v>
+        <v>1703.297</v>
       </c>
     </row>
     <row r="60">
@@ -2570,10 +2570,10 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>3.777</v>
+        <v>654.2140000000001</v>
       </c>
       <c r="C60" t="n">
-        <v>53.562</v>
+        <v>9276.867</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -2582,13 +2582,13 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>14.58</v>
+        <v>2525.209</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>10.332</v>
+        <v>1789.464</v>
       </c>
     </row>
     <row r="61">
@@ -2596,10 +2596,10 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>4.302</v>
+        <v>756.461</v>
       </c>
       <c r="C61" t="n">
-        <v>57.572</v>
+        <v>10122.495</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -2608,13 +2608,13 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>12.087</v>
+        <v>2125.153</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>12.11</v>
+        <v>2129.055</v>
       </c>
     </row>
     <row r="62">
@@ -2622,10 +2622,10 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>5.394</v>
+        <v>923.888</v>
       </c>
       <c r="C62" t="n">
-        <v>59.056</v>
+        <v>10115.913</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -2634,13 +2634,13 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>6.683</v>
+        <v>1144.811</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>13.251</v>
+        <v>2269.77</v>
       </c>
     </row>
     <row r="63">
@@ -2648,10 +2648,10 @@
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>5.037</v>
+        <v>901.71</v>
       </c>
       <c r="C63" t="n">
-        <v>63.114</v>
+        <v>11298.654</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -2660,13 +2660,13 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>8.082000000000001</v>
+        <v>1446.829</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>10.925</v>
+        <v>1955.815</v>
       </c>
     </row>
     <row r="64">
@@ -2674,10 +2674,10 @@
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>5.487</v>
+        <v>1148.386</v>
       </c>
       <c r="C64" t="n">
-        <v>59.155</v>
+        <v>12380.725</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -2686,13 +2686,13 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>9.076000000000001</v>
+        <v>1899.638</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>10.98</v>
+        <v>2298.002</v>
       </c>
     </row>
     <row r="65">
@@ -2700,10 +2700,10 @@
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>4.489</v>
+        <v>963.3680000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>61.43</v>
+        <v>13181.957</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>10.466</v>
+        <v>2245.839</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>9.965999999999999</v>
+        <v>2138.472</v>
       </c>
     </row>
     <row r="66">
@@ -2726,10 +2726,10 @@
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>3.478</v>
+        <v>752.202</v>
       </c>
       <c r="C66" t="n">
-        <v>61.331</v>
+        <v>13263.609</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -2738,13 +2738,13 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>10.344</v>
+        <v>2237.129</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>9.177999999999999</v>
+        <v>1984.853</v>
       </c>
     </row>
     <row r="67">
@@ -2752,10 +2752,10 @@
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>2.909</v>
+        <v>605.71</v>
       </c>
       <c r="C67" t="n">
-        <v>61.616</v>
+        <v>12829.114</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -2764,13 +2764,13 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>10.309</v>
+        <v>2146.43</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>10.102</v>
+        <v>2103.376</v>
       </c>
     </row>
     <row r="68">
@@ -2778,10 +2778,10 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>2.891</v>
+        <v>599.024</v>
       </c>
       <c r="C68" t="n">
-        <v>56.913</v>
+        <v>11793.099</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -2790,13 +2790,13 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>10.297</v>
+        <v>2133.596</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>10.768</v>
+        <v>2231.462</v>
       </c>
     </row>
   </sheetData>
@@ -8683,25 +8683,25 @@
         <v>45658</v>
       </c>
       <c r="B182" t="n">
-        <v>4771</v>
+        <v>787340</v>
       </c>
       <c r="C182" t="n">
-        <v>55387</v>
+        <v>9140709</v>
       </c>
       <c r="D182" t="n">
-        <v>12429</v>
+        <v>2051257</v>
       </c>
       <c r="E182" t="n">
-        <v>9</v>
+        <v>1492</v>
       </c>
       <c r="F182" t="n">
-        <v>13979</v>
+        <v>2307017</v>
       </c>
       <c r="G182" t="n">
-        <v>86575</v>
+        <v>14287815</v>
       </c>
       <c r="H182" t="n">
-        <v>13425</v>
+        <v>2215532</v>
       </c>
     </row>
     <row r="183">
@@ -8709,25 +8709,25 @@
         <v>45689</v>
       </c>
       <c r="B183" t="n">
-        <v>4249</v>
+        <v>727822</v>
       </c>
       <c r="C183" t="n">
-        <v>56950</v>
+        <v>9756024</v>
       </c>
       <c r="D183" t="n">
-        <v>16127</v>
+        <v>2762693</v>
       </c>
       <c r="E183" t="n">
-        <v>37</v>
+        <v>6423</v>
       </c>
       <c r="F183" t="n">
-        <v>11373</v>
+        <v>1948333</v>
       </c>
       <c r="G183" t="n">
-        <v>88736</v>
+        <v>15201295</v>
       </c>
       <c r="H183" t="n">
-        <v>11264</v>
+        <v>1929714</v>
       </c>
     </row>
     <row r="184">
@@ -8735,25 +8735,25 @@
         <v>45717</v>
       </c>
       <c r="B184" t="n">
-        <v>3377</v>
+        <v>697031</v>
       </c>
       <c r="C184" t="n">
-        <v>55872</v>
+        <v>11530851</v>
       </c>
       <c r="D184" t="n">
-        <v>15425</v>
+        <v>3183313</v>
       </c>
       <c r="E184" t="n">
-        <v>11</v>
+        <v>2325</v>
       </c>
       <c r="F184" t="n">
-        <v>10774</v>
+        <v>2223489</v>
       </c>
       <c r="G184" t="n">
-        <v>85459</v>
+        <v>17637010</v>
       </c>
       <c r="H184" t="n">
-        <v>14541</v>
+        <v>3001011</v>
       </c>
     </row>
     <row r="185">
@@ -8761,25 +8761,25 @@
         <v>45748</v>
       </c>
       <c r="B185" t="n">
-        <v>3294</v>
+        <v>655700</v>
       </c>
       <c r="C185" t="n">
-        <v>59662</v>
+        <v>11877540</v>
       </c>
       <c r="D185" t="n">
-        <v>12814</v>
+        <v>2551106</v>
       </c>
       <c r="E185" t="n">
-        <v>14</v>
+        <v>2849</v>
       </c>
       <c r="F185" t="n">
-        <v>10116</v>
+        <v>2013858</v>
       </c>
       <c r="G185" t="n">
-        <v>85900</v>
+        <v>17101053</v>
       </c>
       <c r="H185" t="n">
-        <v>14100</v>
+        <v>2806938</v>
       </c>
     </row>
     <row r="186">
@@ -8787,25 +8787,25 @@
         <v>45778</v>
       </c>
       <c r="B186" t="n">
-        <v>3072</v>
+        <v>627136</v>
       </c>
       <c r="C186" t="n">
-        <v>56835</v>
+        <v>11604010</v>
       </c>
       <c r="D186" t="n">
-        <v>15025</v>
+        <v>3067699</v>
       </c>
       <c r="E186" t="n">
-        <v>13</v>
+        <v>2594</v>
       </c>
       <c r="F186" t="n">
-        <v>9128</v>
+        <v>1863592</v>
       </c>
       <c r="G186" t="n">
-        <v>84072</v>
+        <v>17165031</v>
       </c>
       <c r="H186" t="n">
-        <v>15928</v>
+        <v>3252124</v>
       </c>
     </row>
     <row r="187">
@@ -8813,25 +8813,25 @@
         <v>45809</v>
       </c>
       <c r="B187" t="n">
-        <v>2578</v>
+        <v>504016</v>
       </c>
       <c r="C187" t="n">
-        <v>53015</v>
+        <v>10362877</v>
       </c>
       <c r="D187" t="n">
-        <v>15973</v>
+        <v>3122305</v>
       </c>
       <c r="E187" t="n">
-        <v>8</v>
+        <v>1591</v>
       </c>
       <c r="F187" t="n">
-        <v>10025</v>
+        <v>1959526</v>
       </c>
       <c r="G187" t="n">
-        <v>81600</v>
+        <v>15950316</v>
       </c>
       <c r="H187" t="n">
-        <v>18400</v>
+        <v>3596648</v>
       </c>
     </row>
     <row r="188">
@@ -8839,25 +8839,25 @@
         <v>45839</v>
       </c>
       <c r="B188" t="n">
-        <v>2256</v>
+        <v>445793</v>
       </c>
       <c r="C188" t="n">
-        <v>51684</v>
+        <v>10214604</v>
       </c>
       <c r="D188" t="n">
-        <v>15356</v>
+        <v>3034877</v>
       </c>
       <c r="E188" t="n">
-        <v>26</v>
+        <v>5164</v>
       </c>
       <c r="F188" t="n">
-        <v>10877</v>
+        <v>2149658</v>
       </c>
       <c r="G188" t="n">
-        <v>80199</v>
+        <v>15850096</v>
       </c>
       <c r="H188" t="n">
-        <v>19801</v>
+        <v>3913353</v>
       </c>
     </row>
     <row r="189">
@@ -8865,25 +8865,25 @@
         <v>45870</v>
       </c>
       <c r="B189" t="n">
-        <v>3498</v>
+        <v>703032</v>
       </c>
       <c r="C189" t="n">
-        <v>49261</v>
+        <v>9900312</v>
       </c>
       <c r="D189" t="n">
-        <v>15519</v>
+        <v>3118889</v>
       </c>
       <c r="E189" t="n">
-        <v>12</v>
+        <v>2336</v>
       </c>
       <c r="F189" t="n">
-        <v>9866</v>
+        <v>1982781</v>
       </c>
       <c r="G189" t="n">
-        <v>78155</v>
+        <v>15707349</v>
       </c>
       <c r="H189" t="n">
-        <v>21845</v>
+        <v>4390294</v>
       </c>
     </row>
     <row r="190">
@@ -8891,25 +8891,25 @@
         <v>45901</v>
       </c>
       <c r="B190" t="n">
-        <v>2585</v>
+        <v>493093</v>
       </c>
       <c r="C190" t="n">
-        <v>49425</v>
+        <v>9427883</v>
       </c>
       <c r="D190" t="n">
-        <v>15926</v>
+        <v>3037919</v>
       </c>
       <c r="E190" t="n">
-        <v>18</v>
+        <v>3387</v>
       </c>
       <c r="F190" t="n">
-        <v>8691</v>
+        <v>1657812</v>
       </c>
       <c r="G190" t="n">
-        <v>76645</v>
+        <v>14620093</v>
       </c>
       <c r="H190" t="n">
-        <v>23355</v>
+        <v>4455080</v>
       </c>
     </row>
     <row r="191">
@@ -8917,25 +8917,25 @@
         <v>45931</v>
       </c>
       <c r="B191" t="n">
-        <v>2918</v>
+        <v>567329</v>
       </c>
       <c r="C191" t="n">
-        <v>52055</v>
+        <v>10120218</v>
       </c>
       <c r="D191" t="n">
-        <v>15423</v>
+        <v>2998377</v>
       </c>
       <c r="E191" t="n">
-        <v>20</v>
+        <v>3890</v>
       </c>
       <c r="F191" t="n">
-        <v>8741</v>
+        <v>1699407</v>
       </c>
       <c r="G191" t="n">
-        <v>79157</v>
+        <v>15389221</v>
       </c>
       <c r="H191" t="n">
-        <v>20843</v>
+        <v>4052188</v>
       </c>
     </row>
     <row r="192">
@@ -8943,25 +8943,25 @@
         <v>45962</v>
       </c>
       <c r="B192" t="n">
-        <v>3777</v>
+        <v>654214</v>
       </c>
       <c r="C192" t="n">
-        <v>53562</v>
+        <v>9276867</v>
       </c>
       <c r="D192" t="n">
-        <v>14580</v>
+        <v>2525209</v>
       </c>
       <c r="E192" t="n">
-        <v>104</v>
+        <v>18089</v>
       </c>
       <c r="F192" t="n">
-        <v>10228</v>
+        <v>1771375</v>
       </c>
       <c r="G192" t="n">
-        <v>82252</v>
+        <v>14245755</v>
       </c>
       <c r="H192" t="n">
-        <v>17748</v>
+        <v>3073963</v>
       </c>
     </row>
     <row r="193">
@@ -8969,25 +8969,25 @@
         <v>45992</v>
       </c>
       <c r="B193" t="n">
-        <v>4302</v>
+        <v>756461</v>
       </c>
       <c r="C193" t="n">
-        <v>57572</v>
+        <v>10122495</v>
       </c>
       <c r="D193" t="n">
-        <v>12087</v>
+        <v>2125153</v>
       </c>
       <c r="E193" t="n">
-        <v>473</v>
+        <v>83081</v>
       </c>
       <c r="F193" t="n">
-        <v>11637</v>
+        <v>2045974</v>
       </c>
       <c r="G193" t="n">
-        <v>86071</v>
+        <v>15133164</v>
       </c>
       <c r="H193" t="n">
-        <v>13929</v>
+        <v>2449029</v>
       </c>
     </row>
     <row r="194">
@@ -8995,25 +8995,25 @@
         <v>46023</v>
       </c>
       <c r="B194" t="n">
-        <v>5394</v>
+        <v>923888</v>
       </c>
       <c r="C194" t="n">
-        <v>59056</v>
+        <v>10115913</v>
       </c>
       <c r="D194" t="n">
-        <v>6683</v>
+        <v>1144811</v>
       </c>
       <c r="E194" t="n">
-        <v>264</v>
+        <v>45170</v>
       </c>
       <c r="F194" t="n">
-        <v>12987</v>
+        <v>2224600</v>
       </c>
       <c r="G194" t="n">
-        <v>84384</v>
+        <v>14454381</v>
       </c>
       <c r="H194" t="n">
-        <v>15616</v>
+        <v>2674997</v>
       </c>
     </row>
     <row r="195">
@@ -9021,25 +9021,25 @@
         <v>46054</v>
       </c>
       <c r="B195" t="n">
-        <v>5037</v>
+        <v>901710</v>
       </c>
       <c r="C195" t="n">
-        <v>63114</v>
+        <v>11298654</v>
       </c>
       <c r="D195" t="n">
-        <v>8082</v>
+        <v>1446829</v>
       </c>
       <c r="E195" t="n">
-        <v>4</v>
+        <v>668</v>
       </c>
       <c r="F195" t="n">
-        <v>10921</v>
+        <v>1955147</v>
       </c>
       <c r="G195" t="n">
-        <v>87158</v>
+        <v>15603008</v>
       </c>
       <c r="H195" t="n">
-        <v>12842</v>
+        <v>2298912</v>
       </c>
     </row>
     <row r="196">
@@ -9047,25 +9047,25 @@
         <v>46082</v>
       </c>
       <c r="B196" t="n">
-        <v>5487</v>
+        <v>1148386</v>
       </c>
       <c r="C196" t="n">
-        <v>59155</v>
+        <v>12380725</v>
       </c>
       <c r="D196" t="n">
-        <v>9076</v>
+        <v>1899638</v>
       </c>
       <c r="E196" t="n">
-        <v>6</v>
+        <v>1182</v>
       </c>
       <c r="F196" t="n">
-        <v>10974</v>
+        <v>2296820</v>
       </c>
       <c r="G196" t="n">
-        <v>84699</v>
+        <v>17726751</v>
       </c>
       <c r="H196" t="n">
-        <v>15301</v>
+        <v>3202459</v>
       </c>
     </row>
     <row r="197">
@@ -9073,25 +9073,25 @@
         <v>46113</v>
       </c>
       <c r="B197" t="n">
-        <v>4489</v>
+        <v>963368</v>
       </c>
       <c r="C197" t="n">
-        <v>61430</v>
+        <v>13181957</v>
       </c>
       <c r="D197" t="n">
-        <v>10466</v>
+        <v>2245839</v>
       </c>
       <c r="E197" t="n">
-        <v>10</v>
+        <v>2155</v>
       </c>
       <c r="F197" t="n">
-        <v>9956</v>
+        <v>2136317</v>
       </c>
       <c r="G197" t="n">
-        <v>86351</v>
+        <v>18529636</v>
       </c>
       <c r="H197" t="n">
-        <v>13649</v>
+        <v>2928975</v>
       </c>
     </row>
     <row r="198">
@@ -9099,25 +9099,25 @@
         <v>46143</v>
       </c>
       <c r="B198" t="n">
-        <v>3478</v>
+        <v>752202</v>
       </c>
       <c r="C198" t="n">
-        <v>61331</v>
+        <v>13263609</v>
       </c>
       <c r="D198" t="n">
-        <v>10344</v>
+        <v>2237129</v>
       </c>
       <c r="E198" t="n">
-        <v>13</v>
+        <v>2827</v>
       </c>
       <c r="F198" t="n">
-        <v>9165</v>
+        <v>1982026</v>
       </c>
       <c r="G198" t="n">
-        <v>84331</v>
+        <v>18237792</v>
       </c>
       <c r="H198" t="n">
-        <v>15669</v>
+        <v>3388621</v>
       </c>
     </row>
     <row r="199">
@@ -9125,25 +9125,25 @@
         <v>46174</v>
       </c>
       <c r="B199" t="n">
-        <v>2909</v>
+        <v>605710</v>
       </c>
       <c r="C199" t="n">
-        <v>61616</v>
+        <v>12829114</v>
       </c>
       <c r="D199" t="n">
-        <v>10309</v>
+        <v>2146430</v>
       </c>
       <c r="E199" t="n">
-        <v>30</v>
+        <v>6218</v>
       </c>
       <c r="F199" t="n">
-        <v>10072</v>
+        <v>2097158</v>
       </c>
       <c r="G199" t="n">
-        <v>84937</v>
+        <v>17684630</v>
       </c>
       <c r="H199" t="n">
-        <v>15063</v>
+        <v>3136355</v>
       </c>
     </row>
     <row r="200">
@@ -9151,25 +9151,25 @@
         <v>46204</v>
       </c>
       <c r="B200" t="n">
-        <v>2891</v>
+        <v>599024</v>
       </c>
       <c r="C200" t="n">
-        <v>56913</v>
+        <v>11793099</v>
       </c>
       <c r="D200" t="n">
-        <v>10297</v>
+        <v>2133596</v>
       </c>
       <c r="E200" t="n">
-        <v>123</v>
+        <v>25588</v>
       </c>
       <c r="F200" t="n">
-        <v>10645</v>
+        <v>2205874</v>
       </c>
       <c r="G200" t="n">
-        <v>80869</v>
+        <v>16757181</v>
       </c>
       <c r="H200" t="n">
-        <v>19131</v>
+        <v>3964231</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Peak" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peak" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart - Peak" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Daily" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Peak" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -146,13 +146,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -177,10 +177,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -205,10 +205,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -233,10 +233,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -261,10 +261,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -289,10 +289,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -317,10 +317,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -345,10 +345,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -381,8 +381,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -408,8 +408,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -426,7 +426,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -440,7 +440,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -449,13 +449,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -479,7 +479,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -489,7 +489,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -521,8 +521,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -548,8 +548,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -566,7 +566,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -576,7 +576,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -585,7 +585,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -600,9 +600,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -612,7 +612,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -627,9 +627,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -157,6 +158,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Thailand power generation by fuel (EPPO, whole system) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -460,6 +462,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Thailand monthly peak demand (EGAT system, EPPO) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -961,7 +964,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -983,7 +985,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1058,7 +1059,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1084,7 +1085,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1110,7 +1111,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1136,7 +1137,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1162,7 +1163,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1188,7 +1189,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1214,7 +1215,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1240,7 +1241,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1266,7 +1267,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1292,7 +1293,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1318,7 +1319,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1344,7 +1345,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1370,7 +1371,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1396,7 +1397,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1422,7 +1423,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1448,7 +1449,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1474,7 +1475,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1500,7 +1501,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1526,7 +1527,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1552,7 +1553,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1578,7 +1579,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1604,7 +1605,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1630,7 +1631,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1656,7 +1657,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1682,7 +1683,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1708,7 +1709,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1734,7 +1735,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1760,7 +1761,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1786,7 +1787,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1812,7 +1813,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1838,7 +1839,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1864,7 +1865,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1890,7 +1891,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1916,7 +1917,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1942,7 +1943,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1968,7 +1969,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1994,7 +1995,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2020,7 +2021,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2046,7 +2047,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2072,7 +2073,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2098,7 +2099,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2124,7 +2125,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2150,7 +2151,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2176,7 +2177,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2202,7 +2203,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2228,7 +2229,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2254,7 +2255,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2280,7 +2281,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2306,7 +2307,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2332,7 +2333,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2358,7 +2359,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2384,7 +2385,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2410,7 +2411,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2436,7 +2437,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2462,7 +2463,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2488,7 +2489,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2514,7 +2515,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2540,7 +2541,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2566,7 +2567,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2592,7 +2593,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2618,7 +2619,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2644,7 +2645,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2670,7 +2671,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2696,7 +2697,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2722,7 +2723,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2748,7 +2749,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2774,7 +2775,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2830,7 +2831,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -2838,7 +2839,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -2846,7 +2847,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -2854,7 +2855,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -2862,7 +2863,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -2870,7 +2871,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -2878,7 +2879,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -2886,7 +2887,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -2894,7 +2895,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -2902,7 +2903,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -2910,7 +2911,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -2918,7 +2919,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -2926,7 +2927,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -2934,7 +2935,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -2942,7 +2943,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -2950,7 +2951,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -2958,7 +2959,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -2966,7 +2967,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -2974,7 +2975,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -2982,7 +2983,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -2990,7 +2991,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -2998,7 +2999,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -3006,7 +3007,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -3014,7 +3015,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -3022,7 +3023,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -3030,7 +3031,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -3038,7 +3039,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -3046,7 +3047,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -3054,7 +3055,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -3062,7 +3063,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -3070,7 +3071,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -3078,7 +3079,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -3086,7 +3087,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -3094,7 +3095,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -3102,7 +3103,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -3110,7 +3111,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -3118,7 +3119,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -3126,7 +3127,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -3134,7 +3135,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -3142,7 +3143,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -3150,7 +3151,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -3158,7 +3159,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -3166,7 +3167,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -3174,7 +3175,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -3182,7 +3183,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -3190,7 +3191,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -3198,7 +3199,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -3206,7 +3207,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -3214,7 +3215,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -3222,7 +3223,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -3230,7 +3231,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -3238,7 +3239,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -3246,7 +3247,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -3254,7 +3255,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -3262,7 +3263,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -3270,7 +3271,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -3278,7 +3279,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -3286,7 +3287,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -3294,7 +3295,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -3302,7 +3303,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -3310,7 +3311,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -3318,7 +3319,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -3326,7 +3327,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -3334,7 +3335,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -3342,7 +3343,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -3350,7 +3351,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -3358,7 +3359,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -3366,7 +3367,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -3374,7 +3375,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -3382,7 +3383,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -3390,7 +3391,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="5" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -3398,7 +3399,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="5" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -3406,7 +3407,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -3414,7 +3415,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -3422,7 +3423,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -3430,7 +3431,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -3438,7 +3439,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -3446,7 +3447,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -3454,7 +3455,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -3462,7 +3463,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -3470,7 +3471,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -3478,7 +3479,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -3486,7 +3487,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -3494,7 +3495,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -3502,7 +3503,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -3510,7 +3511,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -3518,7 +3519,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -3526,7 +3527,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -3534,7 +3535,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -3542,7 +3543,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -3550,7 +3551,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -3558,7 +3559,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -3566,7 +3567,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -3574,7 +3575,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -3582,7 +3583,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -3590,7 +3591,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -3598,7 +3599,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -3606,7 +3607,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -3614,7 +3615,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -3622,7 +3623,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -3630,7 +3631,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -3638,7 +3639,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -3646,7 +3647,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -3654,7 +3655,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -3662,7 +3663,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -3670,7 +3671,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -3678,7 +3679,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -3686,7 +3687,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -3694,7 +3695,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -3702,7 +3703,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -3710,7 +3711,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -3718,7 +3719,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -3726,7 +3727,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -3734,7 +3735,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -3742,7 +3743,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -3750,7 +3751,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -3758,7 +3759,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -3766,7 +3767,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -3774,7 +3775,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -3782,7 +3783,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -3790,7 +3791,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -3798,7 +3799,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -3806,7 +3807,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -3814,7 +3815,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -3822,7 +3823,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -3830,7 +3831,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -3838,7 +3839,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -3846,7 +3847,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -3854,7 +3855,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="A130" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -3862,7 +3863,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
+      <c r="A131" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -3870,7 +3871,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
+      <c r="A132" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -3878,7 +3879,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
+      <c r="A133" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -3886,7 +3887,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="A134" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -3894,7 +3895,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
+      <c r="A135" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -3902,7 +3903,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
+      <c r="A136" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -3910,7 +3911,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
+      <c r="A137" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -3918,7 +3919,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
+      <c r="A138" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -3926,7 +3927,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
+      <c r="A139" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -3934,7 +3935,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
+      <c r="A140" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">

--- a/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/thailand_power_generation_daily.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -159,7 +158,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Thailand power generation by fuel (EPPO, whole system) (to Jul/26)</a:t>
+              <a:t>Thailand power generation by fuel (EPPO, whole system) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -189,12 +188,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$68</f>
+              <f>'Chart'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -217,12 +216,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$68</f>
+              <f>'Chart'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -245,12 +244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$68</f>
+              <f>'Chart'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +272,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$68</f>
+              <f>'Chart'!$E$2:$E$69</f>
             </numRef>
           </val>
         </ser>
@@ -301,12 +300,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$68</f>
+              <f>'Chart'!$F$2:$F$69</f>
             </numRef>
           </val>
         </ser>
@@ -329,12 +328,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$68</f>
+              <f>'Chart'!$G$2:$G$69</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +356,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$68</f>
+              <f>'Chart'!$H$2:$H$69</f>
             </numRef>
           </val>
         </ser>
@@ -463,7 +462,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Thailand monthly peak demand (EGAT system, EPPO) (to Jul/26)</a:t>
+              <a:t>Thailand monthly peak demand (EGAT system, EPPO) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -499,12 +498,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Peak'!$A$2:$A$140</f>
+              <f>'Chart - Peak'!$A$2:$A$141</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Peak'!$B$2:$B$140</f>
+              <f>'Chart - Peak'!$B$2:$B$141</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -964,6 +963,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -974,17 +974,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly from 2010-01 to 2026-07, whole Thai system (EGAT, IPP, SPP and VSPP generation), EPPO Table 5.2-4 'Power Generation by Fuel (Detail)', extended with Table 5.2-2 for the current year. EPPO updates about two months after the month.</t>
+          <t>Monthly from 2010-01 to 2026-08, whole Thai system (EGAT, IPP, SPP and VSPP generation), EPPO Table 5.2-4 'Power Generation by Fuel (Detail)', extended with Table 5.2-2 for the current year. EPPO updates about two months after the month.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Files read this run: T05_02_04-1.xls (Last-Modified Mon, 14 Sep 2026 09:30:39 GMT); T05_02_02.xls (Last-Modified Mon, 14 Sep 2026 09:30:04 GMT); T05_02_05-1.xls (Last-Modified Mon, 14 Sep 2026 09:30:50 GMT); T05_02_05.xls (Last-Modified Mon, 14 Sep 2026 09:30:46 GMT)</t>
+          <t>Files read this run: T05_02_04-1.xls (Last-Modified Mon, 14 Sep 2026 09:30:39 GMT); T05_02_02.xls (Last-Modified Sat, 17 Oct 2026 10:23:57 GMT); T05_02_05-1.xls (Last-Modified Mon, 14 Sep 2026 09:30:50 GMT); T05_02_05.xls (Last-Modified Sat, 17 Oct 2026 10:24:06 GMT)</t>
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1059,7 +1060,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1085,7 +1086,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1111,7 +1112,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1137,7 +1138,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1163,7 +1164,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1189,7 +1190,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1215,7 +1216,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1241,7 +1242,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1293,7 +1294,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1319,7 +1320,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1345,7 +1346,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1371,7 +1372,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1397,7 +1398,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1423,7 +1424,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1449,7 +1450,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1475,7 +1476,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1501,7 +1502,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1527,7 +1528,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1553,7 +1554,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1579,7 +1580,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1605,7 +1606,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1631,7 +1632,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1657,7 +1658,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1683,7 +1684,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1709,7 +1710,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1735,7 +1736,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1761,7 +1762,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1787,7 +1788,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1813,7 +1814,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1839,7 +1840,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1865,7 +1866,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1891,7 +1892,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1917,7 +1918,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1943,7 +1944,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1969,7 +1970,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1995,7 +1996,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2021,7 +2022,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2047,7 +2048,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2073,7 +2074,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2099,7 +2100,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2125,7 +2126,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2151,7 +2152,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2177,7 +2178,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2203,7 +2204,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2229,7 +2230,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2255,7 +2256,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2281,7 +2282,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2307,7 +2308,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2333,7 +2334,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2359,7 +2360,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2385,7 +2386,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2411,7 +2412,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2437,7 +2438,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2463,7 +2464,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2489,7 +2490,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2515,7 +2516,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2541,7 +2542,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2567,7 +2568,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2593,7 +2594,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2619,7 +2620,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2645,7 +2646,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2671,7 +2672,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2697,7 +2698,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2723,7 +2724,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2745,11 +2746,11 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1984.853</v>
+        <v>1995.716</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2775,7 +2776,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2797,7 +2798,33 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2231.462</v>
+        <v>2218.357</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>448.101</v>
+      </c>
+      <c r="C69" t="n">
+        <v>12113.48</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2029.91</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2311.482</v>
       </c>
     </row>
   </sheetData>
@@ -2812,7 +2839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B140"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2831,7 +2858,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -2839,7 +2866,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -2847,7 +2874,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -2855,7 +2882,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -2863,7 +2890,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -2871,7 +2898,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -2879,7 +2906,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -2887,7 +2914,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -2895,7 +2922,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -2903,7 +2930,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -2911,7 +2938,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -2919,7 +2946,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -2927,7 +2954,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -2935,7 +2962,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -2943,7 +2970,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -2951,7 +2978,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -2959,7 +2986,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -2967,7 +2994,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -2975,7 +3002,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -2983,7 +3010,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -2991,7 +3018,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -2999,7 +3026,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -3007,7 +3034,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -3015,7 +3042,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -3023,7 +3050,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -3031,7 +3058,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -3039,7 +3066,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -3047,7 +3074,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -3055,7 +3082,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -3063,7 +3090,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -3071,7 +3098,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -3079,7 +3106,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -3087,7 +3114,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -3095,7 +3122,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -3103,7 +3130,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -3111,7 +3138,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -3119,7 +3146,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -3127,7 +3154,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -3135,7 +3162,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -3143,7 +3170,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -3151,7 +3178,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -3159,7 +3186,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -3167,7 +3194,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -3175,7 +3202,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -3183,7 +3210,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -3191,7 +3218,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -3199,7 +3226,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -3207,7 +3234,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -3215,7 +3242,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -3223,7 +3250,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -3231,7 +3258,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -3239,7 +3266,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -3247,7 +3274,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -3255,7 +3282,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -3263,7 +3290,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -3271,7 +3298,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -3279,7 +3306,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -3287,7 +3314,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -3295,7 +3322,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -3303,7 +3330,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -3311,7 +3338,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -3319,7 +3346,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -3327,7 +3354,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -3335,7 +3362,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -3343,7 +3370,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -3351,7 +3378,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -3359,7 +3386,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -3367,7 +3394,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -3375,7 +3402,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -3383,7 +3410,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -3391,7 +3418,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="3" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -3399,7 +3426,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="3" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -3407,7 +3434,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -3415,7 +3442,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -3423,7 +3450,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -3431,7 +3458,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -3439,7 +3466,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -3447,7 +3474,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -3455,7 +3482,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -3463,7 +3490,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -3471,7 +3498,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -3479,7 +3506,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -3487,7 +3514,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -3495,7 +3522,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -3503,7 +3530,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -3511,7 +3538,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -3519,7 +3546,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -3527,7 +3554,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -3535,7 +3562,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -3543,7 +3570,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -3551,7 +3578,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -3559,7 +3586,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -3567,7 +3594,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -3575,7 +3602,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -3583,7 +3610,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -3591,7 +3618,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -3599,7 +3626,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -3607,7 +3634,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -3615,7 +3642,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -3623,7 +3650,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -3631,7 +3658,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -3639,7 +3666,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -3647,7 +3674,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -3655,7 +3682,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -3663,7 +3690,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -3671,7 +3698,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -3679,7 +3706,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -3687,7 +3714,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -3695,7 +3722,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -3703,7 +3730,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -3711,7 +3738,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -3719,7 +3746,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -3727,7 +3754,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -3735,7 +3762,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -3743,7 +3770,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -3751,7 +3778,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -3759,7 +3786,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -3767,7 +3794,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -3775,7 +3802,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -3783,7 +3810,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -3791,7 +3818,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -3799,7 +3826,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -3807,7 +3834,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -3815,7 +3842,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -3823,7 +3850,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -3831,7 +3858,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -3839,7 +3866,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -3847,7 +3874,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -3855,7 +3882,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -3863,7 +3890,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -3871,7 +3898,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -3879,7 +3906,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -3887,7 +3914,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -3895,7 +3922,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -3903,7 +3930,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -3911,7 +3938,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -3919,7 +3946,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -3927,7 +3954,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -3935,11 +3962,19 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">
         <v>32764.2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B141" t="n">
+        <v>32611</v>
       </c>
     </row>
   </sheetData>
@@ -3954,7 +3989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9112,10 +9147,10 @@
         <v>2827</v>
       </c>
       <c r="F198" t="n">
-        <v>1982026</v>
+        <v>1992889</v>
       </c>
       <c r="G198" t="n">
-        <v>18237792</v>
+        <v>18248655</v>
       </c>
       <c r="H198" t="n">
         <v>3388621</v>
@@ -9164,13 +9199,39 @@
         <v>25588</v>
       </c>
       <c r="F200" t="n">
-        <v>2205874</v>
+        <v>2192769</v>
       </c>
       <c r="G200" t="n">
-        <v>16757181</v>
+        <v>16744077</v>
       </c>
       <c r="H200" t="n">
         <v>3964231</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B201" t="n">
+        <v>448101</v>
+      </c>
+      <c r="C201" t="n">
+        <v>12113480</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2029910</v>
+      </c>
+      <c r="E201" t="n">
+        <v>17840</v>
+      </c>
+      <c r="F201" t="n">
+        <v>2293642</v>
+      </c>
+      <c r="G201" t="n">
+        <v>16902973</v>
+      </c>
+      <c r="H201" t="n">
+        <v>3821725</v>
       </c>
     </row>
   </sheetData>
@@ -9184,7 +9245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D200"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11995,6 +12056,20 @@
         <v>80.28088793298717</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B201" t="n">
+        <v>32611</v>
+      </c>
+      <c r="C201" t="n">
+        <v>19572.750741</v>
+      </c>
+      <c r="D201" t="n">
+        <v>80.67051201553799</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
